--- a/artfynd/A 2762-2026 artfynd.xlsx
+++ b/artfynd/A 2762-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131197800</v>
       </c>
       <c r="B2" t="n">
-        <v>79864</v>
+        <v>79865</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>131199510</v>
       </c>
       <c r="B3" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         <v>131198193</v>
       </c>
       <c r="B4" t="n">
-        <v>79864</v>
+        <v>79865</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
         <v>131198456</v>
       </c>
       <c r="B5" t="n">
-        <v>79002</v>
+        <v>79003</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1068,10 +1068,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131198466</v>
+        <v>131198844</v>
       </c>
       <c r="B6" t="n">
-        <v>79835</v>
+        <v>79246</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1079,21 +1079,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1103,10 +1103,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>466092</v>
+        <v>466309</v>
       </c>
       <c r="R6" t="n">
-        <v>6789074</v>
+        <v>6789077</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1165,10 +1165,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131198844</v>
+        <v>131197802</v>
       </c>
       <c r="B7" t="n">
-        <v>79245</v>
+        <v>57881</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1176,34 +1176,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Svalkestjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>466309</v>
+        <v>465938</v>
       </c>
       <c r="R7" t="n">
-        <v>6789077</v>
+        <v>6789021</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1262,10 +1267,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131197802</v>
+        <v>131198466</v>
       </c>
       <c r="B8" t="n">
-        <v>57881</v>
+        <v>79836</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1273,39 +1278,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>229821</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Svalkestjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>465938</v>
+        <v>466092</v>
       </c>
       <c r="R8" t="n">
-        <v>6789021</v>
+        <v>6789074</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1367,7 +1367,7 @@
         <v>131198462</v>
       </c>
       <c r="B9" t="n">
-        <v>79864</v>
+        <v>79865</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1464,7 +1464,7 @@
         <v>131198869</v>
       </c>
       <c r="B10" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1561,7 +1561,7 @@
         <v>131197848</v>
       </c>
       <c r="B11" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1658,7 +1658,7 @@
         <v>131197946</v>
       </c>
       <c r="B12" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1755,7 +1755,7 @@
         <v>131199405</v>
       </c>
       <c r="B13" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1959,7 +1959,7 @@
         <v>131198192</v>
       </c>
       <c r="B15" t="n">
-        <v>79835</v>
+        <v>79836</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2056,7 +2056,7 @@
         <v>131197889</v>
       </c>
       <c r="B16" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2150,10 +2150,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131198252</v>
+        <v>131198195</v>
       </c>
       <c r="B17" t="n">
-        <v>79245</v>
+        <v>57881</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2161,34 +2161,39 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Svalkestjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>466111</v>
+        <v>466050</v>
       </c>
       <c r="R17" t="n">
-        <v>6789063</v>
+        <v>6788971</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2247,10 +2252,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131198195</v>
+        <v>131198252</v>
       </c>
       <c r="B18" t="n">
-        <v>57881</v>
+        <v>79246</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2258,39 +2263,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Svalkestjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>466050</v>
+        <v>466111</v>
       </c>
       <c r="R18" t="n">
-        <v>6788971</v>
+        <v>6789063</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2556,7 +2556,7 @@
         <v>131198708</v>
       </c>
       <c r="B21" t="n">
-        <v>79835</v>
+        <v>79836</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2872,7 +2872,7 @@
         <v>131197797</v>
       </c>
       <c r="B24" t="n">
-        <v>79835</v>
+        <v>79836</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2974,7 +2974,7 @@
         <v>131198447</v>
       </c>
       <c r="B25" t="n">
-        <v>79003</v>
+        <v>79004</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3277,10 +3277,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131198231</v>
+        <v>131199091</v>
       </c>
       <c r="B28" t="n">
-        <v>79245</v>
+        <v>57884</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3288,37 +3288,42 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Svalkestjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>466052</v>
+        <v>466114</v>
       </c>
       <c r="R28" t="n">
-        <v>6789006</v>
+        <v>6788962</v>
       </c>
       <c r="S28" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3352,7 +3357,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Rikligt till måttligt i en radie av ca 50 meter  1 bild gren i förgrund</t>
+          <t>2 bild, tall med gran till vänster.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3379,10 +3384,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131199091</v>
+        <v>131198231</v>
       </c>
       <c r="B29" t="n">
-        <v>57884</v>
+        <v>79246</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3390,42 +3395,37 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Svalkestjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>466114</v>
+        <v>466052</v>
       </c>
       <c r="R29" t="n">
-        <v>6788962</v>
+        <v>6789006</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3459,7 +3459,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>2 bild, tall med gran till vänster.</t>
+          <t>Rikligt till måttligt i en radie av ca 50 meter  1 bild gren i förgrund</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3486,10 +3486,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131198787</v>
+        <v>131197782</v>
       </c>
       <c r="B30" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3521,10 +3521,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>466290</v>
+        <v>465938</v>
       </c>
       <c r="R30" t="n">
-        <v>6789094</v>
+        <v>6789011</v>
       </c>
       <c r="S30" t="n">
         <v>50</v>
@@ -3561,7 +3561,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Rikligt i en radie av ca 50 meter  1 bild</t>
+          <t>Rikligt till måttligt i en radie av ca 50 meter. 3 bilder på tallar</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3588,10 +3588,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131197782</v>
+        <v>131198787</v>
       </c>
       <c r="B31" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3623,10 +3623,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>465938</v>
+        <v>466290</v>
       </c>
       <c r="R31" t="n">
-        <v>6789011</v>
+        <v>6789094</v>
       </c>
       <c r="S31" t="n">
         <v>50</v>
@@ -3663,7 +3663,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Rikligt till måttligt i en radie av ca 50 meter. 3 bilder på tallar</t>
+          <t>Rikligt i en radie av ca 50 meter  1 bild</t>
         </is>
       </c>
       <c r="AD31" t="b">

--- a/artfynd/A 2762-2026 artfynd.xlsx
+++ b/artfynd/A 2762-2026 artfynd.xlsx
@@ -2150,10 +2150,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131198195</v>
+        <v>131198252</v>
       </c>
       <c r="B17" t="n">
-        <v>57881</v>
+        <v>79246</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2161,39 +2161,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Svalkestjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>466050</v>
+        <v>466111</v>
       </c>
       <c r="R17" t="n">
-        <v>6788971</v>
+        <v>6789063</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2252,10 +2247,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131198252</v>
+        <v>131198195</v>
       </c>
       <c r="B18" t="n">
-        <v>79246</v>
+        <v>57881</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2263,34 +2258,39 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Svalkestjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>466111</v>
+        <v>466050</v>
       </c>
       <c r="R18" t="n">
-        <v>6789063</v>
+        <v>6788971</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -3277,10 +3277,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131199091</v>
+        <v>131198231</v>
       </c>
       <c r="B28" t="n">
-        <v>57884</v>
+        <v>79246</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3288,42 +3288,37 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Svalkestjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>466114</v>
+        <v>466052</v>
       </c>
       <c r="R28" t="n">
-        <v>6788962</v>
+        <v>6789006</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3357,7 +3352,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>2 bild, tall med gran till vänster.</t>
+          <t>Rikligt till måttligt i en radie av ca 50 meter  1 bild gren i förgrund</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3384,10 +3379,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131198231</v>
+        <v>131199091</v>
       </c>
       <c r="B29" t="n">
-        <v>79246</v>
+        <v>57884</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3395,37 +3390,42 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Svalkestjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>466052</v>
+        <v>466114</v>
       </c>
       <c r="R29" t="n">
-        <v>6789006</v>
+        <v>6788962</v>
       </c>
       <c r="S29" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3459,7 +3459,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Rikligt till måttligt i en radie av ca 50 meter  1 bild gren i förgrund</t>
+          <t>2 bild, tall med gran till vänster.</t>
         </is>
       </c>
       <c r="AD29" t="b">

--- a/artfynd/A 2762-2026 artfynd.xlsx
+++ b/artfynd/A 2762-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131197800</v>
       </c>
       <c r="B2" t="n">
-        <v>79865</v>
+        <v>79867</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>131199510</v>
       </c>
       <c r="B3" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         <v>131198193</v>
       </c>
       <c r="B4" t="n">
-        <v>79865</v>
+        <v>79867</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
         <v>131198456</v>
       </c>
       <c r="B5" t="n">
-        <v>79003</v>
+        <v>79005</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
         <v>131198844</v>
       </c>
       <c r="B6" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1168,7 +1168,7 @@
         <v>131197802</v>
       </c>
       <c r="B7" t="n">
-        <v>57881</v>
+        <v>57883</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1270,7 +1270,7 @@
         <v>131198466</v>
       </c>
       <c r="B8" t="n">
-        <v>79836</v>
+        <v>79838</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1367,7 +1367,7 @@
         <v>131198462</v>
       </c>
       <c r="B9" t="n">
-        <v>79865</v>
+        <v>79867</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1464,7 +1464,7 @@
         <v>131198869</v>
       </c>
       <c r="B10" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1561,7 +1561,7 @@
         <v>131197848</v>
       </c>
       <c r="B11" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1658,7 +1658,7 @@
         <v>131197946</v>
       </c>
       <c r="B12" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1755,7 +1755,7 @@
         <v>131199405</v>
       </c>
       <c r="B13" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1959,7 +1959,7 @@
         <v>131198192</v>
       </c>
       <c r="B15" t="n">
-        <v>79836</v>
+        <v>79838</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2056,7 +2056,7 @@
         <v>131197889</v>
       </c>
       <c r="B16" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2153,7 +2153,7 @@
         <v>131198252</v>
       </c>
       <c r="B17" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2250,7 +2250,7 @@
         <v>131198195</v>
       </c>
       <c r="B18" t="n">
-        <v>57881</v>
+        <v>57883</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2454,7 +2454,7 @@
         <v>131197847</v>
       </c>
       <c r="B20" t="n">
-        <v>57881</v>
+        <v>57883</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2556,7 +2556,7 @@
         <v>131198708</v>
       </c>
       <c r="B21" t="n">
-        <v>79836</v>
+        <v>79838</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2658,7 +2658,7 @@
         <v>131198867</v>
       </c>
       <c r="B22" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2765,7 +2765,7 @@
         <v>131198842</v>
       </c>
       <c r="B23" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2872,7 +2872,7 @@
         <v>131197797</v>
       </c>
       <c r="B24" t="n">
-        <v>79836</v>
+        <v>79838</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2974,7 +2974,7 @@
         <v>131198447</v>
       </c>
       <c r="B25" t="n">
-        <v>79004</v>
+        <v>79006</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3076,7 +3076,7 @@
         <v>131198249</v>
       </c>
       <c r="B26" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3280,7 +3280,7 @@
         <v>131198231</v>
       </c>
       <c r="B28" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3382,7 +3382,7 @@
         <v>131199091</v>
       </c>
       <c r="B29" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3486,10 +3486,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131197782</v>
+        <v>131198787</v>
       </c>
       <c r="B30" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3521,10 +3521,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>465938</v>
+        <v>466290</v>
       </c>
       <c r="R30" t="n">
-        <v>6789011</v>
+        <v>6789094</v>
       </c>
       <c r="S30" t="n">
         <v>50</v>
@@ -3561,7 +3561,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Rikligt till måttligt i en radie av ca 50 meter. 3 bilder på tallar</t>
+          <t>Rikligt i en radie av ca 50 meter  1 bild</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3588,10 +3588,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131198787</v>
+        <v>131197782</v>
       </c>
       <c r="B31" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3623,10 +3623,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>466290</v>
+        <v>465938</v>
       </c>
       <c r="R31" t="n">
-        <v>6789094</v>
+        <v>6789011</v>
       </c>
       <c r="S31" t="n">
         <v>50</v>
@@ -3663,7 +3663,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Rikligt i en radie av ca 50 meter  1 bild</t>
+          <t>Rikligt till måttligt i en radie av ca 50 meter. 3 bilder på tallar</t>
         </is>
       </c>
       <c r="AD31" t="b">

--- a/artfynd/A 2762-2026 artfynd.xlsx
+++ b/artfynd/A 2762-2026 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131197800</v>
+        <v>131199510</v>
       </c>
       <c r="B2" t="n">
-        <v>79867</v>
+        <v>79249</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>465938</v>
+        <v>465892</v>
       </c>
       <c r="R2" t="n">
-        <v>6789021</v>
+        <v>6789046</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -746,6 +746,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2026-02-17</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Rikligt till måttligt i en radie av ca 50 meter, synfältet</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -772,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131199510</v>
+        <v>131197800</v>
       </c>
       <c r="B3" t="n">
-        <v>79248</v>
+        <v>79868</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +788,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>465892</v>
+        <v>465938</v>
       </c>
       <c r="R3" t="n">
-        <v>6789046</v>
+        <v>6789021</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -843,11 +848,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2026-02-17</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Rikligt till måttligt i en radie av ca 50 meter, synfältet</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -877,7 +877,7 @@
         <v>131198193</v>
       </c>
       <c r="B4" t="n">
-        <v>79867</v>
+        <v>79868</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
         <v>131198456</v>
       </c>
       <c r="B5" t="n">
-        <v>79005</v>
+        <v>79006</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1068,10 +1068,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131198844</v>
+        <v>131197802</v>
       </c>
       <c r="B6" t="n">
-        <v>79248</v>
+        <v>57884</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1079,34 +1079,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Svalkestjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>466309</v>
+        <v>465938</v>
       </c>
       <c r="R6" t="n">
-        <v>6789077</v>
+        <v>6789021</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1165,10 +1170,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131197802</v>
+        <v>131198844</v>
       </c>
       <c r="B7" t="n">
-        <v>57883</v>
+        <v>79249</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1176,39 +1181,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Svalkestjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>465938</v>
+        <v>466309</v>
       </c>
       <c r="R7" t="n">
-        <v>6789021</v>
+        <v>6789077</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1270,7 +1270,7 @@
         <v>131198466</v>
       </c>
       <c r="B8" t="n">
-        <v>79838</v>
+        <v>79839</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1367,7 +1367,7 @@
         <v>131198462</v>
       </c>
       <c r="B9" t="n">
-        <v>79867</v>
+        <v>79868</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1464,7 +1464,7 @@
         <v>131198869</v>
       </c>
       <c r="B10" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1561,7 +1561,7 @@
         <v>131197848</v>
       </c>
       <c r="B11" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1658,7 +1658,7 @@
         <v>131197946</v>
       </c>
       <c r="B12" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1755,7 +1755,7 @@
         <v>131199405</v>
       </c>
       <c r="B13" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1959,7 +1959,7 @@
         <v>131198192</v>
       </c>
       <c r="B15" t="n">
-        <v>79838</v>
+        <v>79839</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2056,7 +2056,7 @@
         <v>131197889</v>
       </c>
       <c r="B16" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2153,7 +2153,7 @@
         <v>131198252</v>
       </c>
       <c r="B17" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2250,7 +2250,7 @@
         <v>131198195</v>
       </c>
       <c r="B18" t="n">
-        <v>57883</v>
+        <v>57884</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2454,7 +2454,7 @@
         <v>131197847</v>
       </c>
       <c r="B20" t="n">
-        <v>57883</v>
+        <v>57884</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2556,7 +2556,7 @@
         <v>131198708</v>
       </c>
       <c r="B21" t="n">
-        <v>79838</v>
+        <v>79839</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2658,7 +2658,7 @@
         <v>131198867</v>
       </c>
       <c r="B22" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2765,7 +2765,7 @@
         <v>131198842</v>
       </c>
       <c r="B23" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2872,7 +2872,7 @@
         <v>131197797</v>
       </c>
       <c r="B24" t="n">
-        <v>79838</v>
+        <v>79839</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2974,7 +2974,7 @@
         <v>131198447</v>
       </c>
       <c r="B25" t="n">
-        <v>79006</v>
+        <v>79007</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3076,7 +3076,7 @@
         <v>131198249</v>
       </c>
       <c r="B26" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3280,7 +3280,7 @@
         <v>131198231</v>
       </c>
       <c r="B28" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3382,7 +3382,7 @@
         <v>131199091</v>
       </c>
       <c r="B29" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3489,7 +3489,7 @@
         <v>131198787</v>
       </c>
       <c r="B30" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3591,7 +3591,7 @@
         <v>131197782</v>
       </c>
       <c r="B31" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>

--- a/artfynd/A 2762-2026 artfynd.xlsx
+++ b/artfynd/A 2762-2026 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131199510</v>
+        <v>131197800</v>
       </c>
       <c r="B2" t="n">
-        <v>79249</v>
+        <v>79868</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>465892</v>
+        <v>465938</v>
       </c>
       <c r="R2" t="n">
-        <v>6789046</v>
+        <v>6789021</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -746,11 +746,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2026-02-17</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Rikligt till måttligt i en radie av ca 50 meter, synfältet</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131197800</v>
+        <v>131199510</v>
       </c>
       <c r="B3" t="n">
-        <v>79868</v>
+        <v>79249</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -788,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -812,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>465938</v>
+        <v>465892</v>
       </c>
       <c r="R3" t="n">
-        <v>6789021</v>
+        <v>6789046</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -848,6 +843,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2026-02-17</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Rikligt till måttligt i en radie av ca 50 meter, synfältet</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1068,10 +1068,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131197802</v>
+        <v>131198466</v>
       </c>
       <c r="B6" t="n">
-        <v>57884</v>
+        <v>79839</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1079,39 +1079,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>229821</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Svalkestjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>465938</v>
+        <v>466092</v>
       </c>
       <c r="R6" t="n">
-        <v>6789021</v>
+        <v>6789074</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1170,10 +1165,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131198844</v>
+        <v>131197802</v>
       </c>
       <c r="B7" t="n">
-        <v>79249</v>
+        <v>57884</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1181,34 +1176,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Svalkestjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>466309</v>
+        <v>465938</v>
       </c>
       <c r="R7" t="n">
-        <v>6789077</v>
+        <v>6789021</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1267,10 +1267,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131198466</v>
+        <v>131198844</v>
       </c>
       <c r="B8" t="n">
-        <v>79839</v>
+        <v>79249</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1278,21 +1278,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1302,10 +1302,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>466092</v>
+        <v>466309</v>
       </c>
       <c r="R8" t="n">
-        <v>6789074</v>
+        <v>6789077</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -3277,10 +3277,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131198231</v>
+        <v>131199091</v>
       </c>
       <c r="B28" t="n">
-        <v>79249</v>
+        <v>57887</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3288,37 +3288,42 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Svalkestjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>466052</v>
+        <v>466114</v>
       </c>
       <c r="R28" t="n">
-        <v>6789006</v>
+        <v>6788962</v>
       </c>
       <c r="S28" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3352,7 +3357,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Rikligt till måttligt i en radie av ca 50 meter  1 bild gren i förgrund</t>
+          <t>2 bild, tall med gran till vänster.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3379,10 +3384,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131199091</v>
+        <v>131198231</v>
       </c>
       <c r="B29" t="n">
-        <v>57887</v>
+        <v>79249</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3390,42 +3395,37 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Svalkestjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>466114</v>
+        <v>466052</v>
       </c>
       <c r="R29" t="n">
-        <v>6788962</v>
+        <v>6789006</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3459,7 +3459,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>2 bild, tall med gran till vänster.</t>
+          <t>Rikligt till måttligt i en radie av ca 50 meter  1 bild gren i förgrund</t>
         </is>
       </c>
       <c r="AD29" t="b">

--- a/artfynd/A 2762-2026 artfynd.xlsx
+++ b/artfynd/A 2762-2026 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131197800</v>
+        <v>131199510</v>
       </c>
       <c r="B2" t="n">
-        <v>79868</v>
+        <v>79249</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>465938</v>
+        <v>465892</v>
       </c>
       <c r="R2" t="n">
-        <v>6789021</v>
+        <v>6789046</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -746,6 +746,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2026-02-17</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Rikligt till måttligt i en radie av ca 50 meter, synfältet</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -772,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131199510</v>
+        <v>131197800</v>
       </c>
       <c r="B3" t="n">
-        <v>79249</v>
+        <v>79868</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +788,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>465892</v>
+        <v>465938</v>
       </c>
       <c r="R3" t="n">
-        <v>6789046</v>
+        <v>6789021</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -843,11 +848,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2026-02-17</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Rikligt till måttligt i en radie av ca 50 meter, synfältet</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1068,10 +1068,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131198466</v>
+        <v>131198844</v>
       </c>
       <c r="B6" t="n">
-        <v>79839</v>
+        <v>79249</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1079,21 +1079,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1103,10 +1103,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>466092</v>
+        <v>466309</v>
       </c>
       <c r="R6" t="n">
-        <v>6789074</v>
+        <v>6789077</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1267,10 +1267,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131198844</v>
+        <v>131198466</v>
       </c>
       <c r="B8" t="n">
-        <v>79249</v>
+        <v>79839</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1278,21 +1278,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1302,10 +1302,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>466309</v>
+        <v>466092</v>
       </c>
       <c r="R8" t="n">
-        <v>6789077</v>
+        <v>6789074</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -3277,10 +3277,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131199091</v>
+        <v>131198231</v>
       </c>
       <c r="B28" t="n">
-        <v>57887</v>
+        <v>79249</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3288,42 +3288,37 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Svalkestjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>466114</v>
+        <v>466052</v>
       </c>
       <c r="R28" t="n">
-        <v>6788962</v>
+        <v>6789006</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3357,7 +3352,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>2 bild, tall med gran till vänster.</t>
+          <t>Rikligt till måttligt i en radie av ca 50 meter  1 bild gren i förgrund</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3384,10 +3379,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131198231</v>
+        <v>131199091</v>
       </c>
       <c r="B29" t="n">
-        <v>79249</v>
+        <v>57887</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3395,37 +3390,42 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Svalkestjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>466052</v>
+        <v>466114</v>
       </c>
       <c r="R29" t="n">
-        <v>6789006</v>
+        <v>6788962</v>
       </c>
       <c r="S29" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3459,7 +3459,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Rikligt till måttligt i en radie av ca 50 meter  1 bild gren i förgrund</t>
+          <t>2 bild, tall med gran till vänster.</t>
         </is>
       </c>
       <c r="AD29" t="b">

--- a/artfynd/A 2762-2026 artfynd.xlsx
+++ b/artfynd/A 2762-2026 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131199510</v>
+        <v>131197800</v>
       </c>
       <c r="B2" t="n">
-        <v>79249</v>
+        <v>79869</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>465892</v>
+        <v>465938</v>
       </c>
       <c r="R2" t="n">
-        <v>6789046</v>
+        <v>6789021</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -746,11 +746,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2026-02-17</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Rikligt till måttligt i en radie av ca 50 meter, synfältet</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131197800</v>
+        <v>131199510</v>
       </c>
       <c r="B3" t="n">
-        <v>79868</v>
+        <v>79250</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -788,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -812,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>465938</v>
+        <v>465892</v>
       </c>
       <c r="R3" t="n">
-        <v>6789021</v>
+        <v>6789046</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -848,6 +843,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2026-02-17</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Rikligt till måttligt i en radie av ca 50 meter, synfältet</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -877,7 +877,7 @@
         <v>131198193</v>
       </c>
       <c r="B4" t="n">
-        <v>79868</v>
+        <v>79869</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
         <v>131198456</v>
       </c>
       <c r="B5" t="n">
-        <v>79006</v>
+        <v>79007</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1068,10 +1068,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131198844</v>
+        <v>131197802</v>
       </c>
       <c r="B6" t="n">
-        <v>79249</v>
+        <v>57885</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1079,34 +1079,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Svalkestjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>466309</v>
+        <v>465938</v>
       </c>
       <c r="R6" t="n">
-        <v>6789077</v>
+        <v>6789021</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1165,10 +1170,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131197802</v>
+        <v>131198844</v>
       </c>
       <c r="B7" t="n">
-        <v>57884</v>
+        <v>79250</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1176,39 +1181,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Svalkestjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>465938</v>
+        <v>466309</v>
       </c>
       <c r="R7" t="n">
-        <v>6789021</v>
+        <v>6789077</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1270,7 +1270,7 @@
         <v>131198466</v>
       </c>
       <c r="B8" t="n">
-        <v>79839</v>
+        <v>79840</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1367,7 +1367,7 @@
         <v>131198462</v>
       </c>
       <c r="B9" t="n">
-        <v>79868</v>
+        <v>79869</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1464,7 +1464,7 @@
         <v>131198869</v>
       </c>
       <c r="B10" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1561,7 +1561,7 @@
         <v>131197848</v>
       </c>
       <c r="B11" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1658,7 +1658,7 @@
         <v>131197946</v>
       </c>
       <c r="B12" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1755,7 +1755,7 @@
         <v>131199405</v>
       </c>
       <c r="B13" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1959,7 +1959,7 @@
         <v>131198192</v>
       </c>
       <c r="B15" t="n">
-        <v>79839</v>
+        <v>79840</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2056,7 +2056,7 @@
         <v>131197889</v>
       </c>
       <c r="B16" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2150,10 +2150,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131198252</v>
+        <v>131198195</v>
       </c>
       <c r="B17" t="n">
-        <v>79249</v>
+        <v>57885</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2161,34 +2161,39 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Svalkestjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>466111</v>
+        <v>466050</v>
       </c>
       <c r="R17" t="n">
-        <v>6789063</v>
+        <v>6788971</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2247,10 +2252,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131198195</v>
+        <v>131198252</v>
       </c>
       <c r="B18" t="n">
-        <v>57884</v>
+        <v>79250</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2258,39 +2263,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Svalkestjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>466050</v>
+        <v>466111</v>
       </c>
       <c r="R18" t="n">
-        <v>6788971</v>
+        <v>6789063</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2454,7 +2454,7 @@
         <v>131197847</v>
       </c>
       <c r="B20" t="n">
-        <v>57884</v>
+        <v>57885</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2556,7 +2556,7 @@
         <v>131198708</v>
       </c>
       <c r="B21" t="n">
-        <v>79839</v>
+        <v>79840</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2658,7 +2658,7 @@
         <v>131198867</v>
       </c>
       <c r="B22" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2765,7 +2765,7 @@
         <v>131198842</v>
       </c>
       <c r="B23" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2872,7 +2872,7 @@
         <v>131197797</v>
       </c>
       <c r="B24" t="n">
-        <v>79839</v>
+        <v>79840</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2974,7 +2974,7 @@
         <v>131198447</v>
       </c>
       <c r="B25" t="n">
-        <v>79007</v>
+        <v>79008</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3073,53 +3073,48 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131198249</v>
+        <v>131197961</v>
       </c>
       <c r="B26" t="n">
-        <v>57887</v>
+        <v>8451</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>106545</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Svalkestjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>466111</v>
+        <v>466023</v>
       </c>
       <c r="R26" t="n">
-        <v>6789063</v>
+        <v>6788957</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3149,11 +3144,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2026-02-17</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>2 bild. Avbarkad gran</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3180,48 +3170,53 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131197961</v>
+        <v>131198249</v>
       </c>
       <c r="B27" t="n">
-        <v>8451</v>
+        <v>57888</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>106545</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Svalkestjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>466023</v>
+        <v>466111</v>
       </c>
       <c r="R27" t="n">
-        <v>6788957</v>
+        <v>6789063</v>
       </c>
       <c r="S27" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3251,6 +3246,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2026-02-17</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>2 bild. Avbarkad gran</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3277,10 +3277,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131198231</v>
+        <v>131199091</v>
       </c>
       <c r="B28" t="n">
-        <v>79249</v>
+        <v>57888</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3288,37 +3288,42 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Svalkestjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>466052</v>
+        <v>466114</v>
       </c>
       <c r="R28" t="n">
-        <v>6789006</v>
+        <v>6788962</v>
       </c>
       <c r="S28" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3352,7 +3357,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Rikligt till måttligt i en radie av ca 50 meter  1 bild gren i förgrund</t>
+          <t>2 bild, tall med gran till vänster.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3379,10 +3384,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131199091</v>
+        <v>131198231</v>
       </c>
       <c r="B29" t="n">
-        <v>57887</v>
+        <v>79250</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3390,42 +3395,37 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Svalkestjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>466114</v>
+        <v>466052</v>
       </c>
       <c r="R29" t="n">
-        <v>6788962</v>
+        <v>6789006</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3459,7 +3459,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>2 bild, tall med gran till vänster.</t>
+          <t>Rikligt till måttligt i en radie av ca 50 meter  1 bild gren i förgrund</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3489,7 +3489,7 @@
         <v>131198787</v>
       </c>
       <c r="B30" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3591,7 +3591,7 @@
         <v>131197782</v>
       </c>
       <c r="B31" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>

--- a/artfynd/A 2762-2026 artfynd.xlsx
+++ b/artfynd/A 2762-2026 artfynd.xlsx
@@ -874,10 +874,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131198193</v>
+        <v>131198456</v>
       </c>
       <c r="B4" t="n">
-        <v>79869</v>
+        <v>79007</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -885,21 +885,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -909,10 +909,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>466050</v>
+        <v>466092</v>
       </c>
       <c r="R4" t="n">
-        <v>6788971</v>
+        <v>6789074</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -971,10 +971,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131198456</v>
+        <v>131198193</v>
       </c>
       <c r="B5" t="n">
-        <v>79007</v>
+        <v>79869</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -982,21 +982,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1006,10 +1006,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>466092</v>
+        <v>466050</v>
       </c>
       <c r="R5" t="n">
-        <v>6789074</v>
+        <v>6788971</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1068,10 +1068,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131197802</v>
+        <v>131198844</v>
       </c>
       <c r="B6" t="n">
-        <v>57885</v>
+        <v>79250</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1079,39 +1079,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Svalkestjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>465938</v>
+        <v>466309</v>
       </c>
       <c r="R6" t="n">
-        <v>6789021</v>
+        <v>6789077</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1170,10 +1165,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131198844</v>
+        <v>131197802</v>
       </c>
       <c r="B7" t="n">
-        <v>79250</v>
+        <v>57885</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1181,34 +1176,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Svalkestjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>466309</v>
+        <v>465938</v>
       </c>
       <c r="R7" t="n">
-        <v>6789077</v>
+        <v>6789021</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>

--- a/artfynd/A 2762-2026 artfynd.xlsx
+++ b/artfynd/A 2762-2026 artfynd.xlsx
@@ -2150,10 +2150,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131198195</v>
+        <v>131198252</v>
       </c>
       <c r="B17" t="n">
-        <v>57885</v>
+        <v>79250</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2161,39 +2161,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Svalkestjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>466050</v>
+        <v>466111</v>
       </c>
       <c r="R17" t="n">
-        <v>6788971</v>
+        <v>6789063</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2252,10 +2247,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131198252</v>
+        <v>131198195</v>
       </c>
       <c r="B18" t="n">
-        <v>79250</v>
+        <v>57885</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2263,34 +2258,39 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Svalkestjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>466111</v>
+        <v>466050</v>
       </c>
       <c r="R18" t="n">
-        <v>6789063</v>
+        <v>6788971</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>

--- a/artfynd/A 2762-2026 artfynd.xlsx
+++ b/artfynd/A 2762-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131197800</v>
       </c>
       <c r="B2" t="n">
-        <v>79869</v>
+        <v>79872</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>131199510</v>
       </c>
       <c r="B3" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -874,10 +874,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131198456</v>
+        <v>131198193</v>
       </c>
       <c r="B4" t="n">
-        <v>79007</v>
+        <v>79872</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -885,21 +885,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -909,10 +909,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>466092</v>
+        <v>466050</v>
       </c>
       <c r="R4" t="n">
-        <v>6789074</v>
+        <v>6788971</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -971,10 +971,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131198193</v>
+        <v>131198456</v>
       </c>
       <c r="B5" t="n">
-        <v>79869</v>
+        <v>79010</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -982,21 +982,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1006,10 +1006,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>466050</v>
+        <v>466092</v>
       </c>
       <c r="R5" t="n">
-        <v>6788971</v>
+        <v>6789074</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1068,10 +1068,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131198844</v>
+        <v>131197802</v>
       </c>
       <c r="B6" t="n">
-        <v>79250</v>
+        <v>57888</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1079,34 +1079,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Svalkestjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>466309</v>
+        <v>465938</v>
       </c>
       <c r="R6" t="n">
-        <v>6789077</v>
+        <v>6789021</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1165,10 +1170,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131197802</v>
+        <v>131198844</v>
       </c>
       <c r="B7" t="n">
-        <v>57885</v>
+        <v>79253</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1176,39 +1181,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Svalkestjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>465938</v>
+        <v>466309</v>
       </c>
       <c r="R7" t="n">
-        <v>6789021</v>
+        <v>6789077</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1270,7 +1270,7 @@
         <v>131198466</v>
       </c>
       <c r="B8" t="n">
-        <v>79840</v>
+        <v>79843</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1367,7 +1367,7 @@
         <v>131198462</v>
       </c>
       <c r="B9" t="n">
-        <v>79869</v>
+        <v>79872</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1461,10 +1461,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131198869</v>
+        <v>131197848</v>
       </c>
       <c r="B10" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1496,10 +1496,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>466309</v>
+        <v>465971</v>
       </c>
       <c r="R10" t="n">
-        <v>6789065</v>
+        <v>6788983</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1558,10 +1558,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131197848</v>
+        <v>131198869</v>
       </c>
       <c r="B11" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1593,10 +1593,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>465971</v>
+        <v>466309</v>
       </c>
       <c r="R11" t="n">
-        <v>6788983</v>
+        <v>6789065</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1658,7 +1658,7 @@
         <v>131197946</v>
       </c>
       <c r="B12" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1755,7 +1755,7 @@
         <v>131199405</v>
       </c>
       <c r="B13" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1852,7 +1852,7 @@
         <v>131199508</v>
       </c>
       <c r="B14" t="n">
-        <v>8451</v>
+        <v>8453</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1959,7 +1959,7 @@
         <v>131198192</v>
       </c>
       <c r="B15" t="n">
-        <v>79840</v>
+        <v>79843</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2056,7 +2056,7 @@
         <v>131197889</v>
       </c>
       <c r="B16" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2153,7 +2153,7 @@
         <v>131198252</v>
       </c>
       <c r="B17" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2250,7 +2250,7 @@
         <v>131198195</v>
       </c>
       <c r="B18" t="n">
-        <v>57885</v>
+        <v>57888</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2352,7 +2352,7 @@
         <v>131197888</v>
       </c>
       <c r="B19" t="n">
-        <v>8451</v>
+        <v>8453</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2454,7 +2454,7 @@
         <v>131197847</v>
       </c>
       <c r="B20" t="n">
-        <v>57885</v>
+        <v>57888</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2556,7 +2556,7 @@
         <v>131198708</v>
       </c>
       <c r="B21" t="n">
-        <v>79840</v>
+        <v>79843</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2658,7 +2658,7 @@
         <v>131198867</v>
       </c>
       <c r="B22" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2765,7 +2765,7 @@
         <v>131198842</v>
       </c>
       <c r="B23" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2872,7 +2872,7 @@
         <v>131197797</v>
       </c>
       <c r="B24" t="n">
-        <v>79840</v>
+        <v>79843</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2974,7 +2974,7 @@
         <v>131198447</v>
       </c>
       <c r="B25" t="n">
-        <v>79008</v>
+        <v>79011</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3073,48 +3073,53 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131197961</v>
+        <v>131198249</v>
       </c>
       <c r="B26" t="n">
-        <v>8451</v>
+        <v>57891</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>106545</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Svalkestjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>466023</v>
+        <v>466111</v>
       </c>
       <c r="R26" t="n">
-        <v>6788957</v>
+        <v>6789063</v>
       </c>
       <c r="S26" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3144,6 +3149,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2026-02-17</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>2 bild. Avbarkad gran</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3170,53 +3180,48 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131198249</v>
+        <v>131197961</v>
       </c>
       <c r="B27" t="n">
-        <v>57888</v>
+        <v>8453</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>106545</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Svalkestjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>466111</v>
+        <v>466023</v>
       </c>
       <c r="R27" t="n">
-        <v>6789063</v>
+        <v>6788957</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3246,11 +3251,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2026-02-17</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>2 bild. Avbarkad gran</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3277,10 +3277,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131199091</v>
+        <v>131198231</v>
       </c>
       <c r="B28" t="n">
-        <v>57888</v>
+        <v>79253</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3288,42 +3288,37 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Svalkestjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>466114</v>
+        <v>466052</v>
       </c>
       <c r="R28" t="n">
-        <v>6788962</v>
+        <v>6789006</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3357,7 +3352,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>2 bild, tall med gran till vänster.</t>
+          <t>Rikligt till måttligt i en radie av ca 50 meter  1 bild gren i förgrund</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3384,10 +3379,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131198231</v>
+        <v>131199091</v>
       </c>
       <c r="B29" t="n">
-        <v>79250</v>
+        <v>57891</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3395,37 +3390,42 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Svalkestjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>466052</v>
+        <v>466114</v>
       </c>
       <c r="R29" t="n">
-        <v>6789006</v>
+        <v>6788962</v>
       </c>
       <c r="S29" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3459,7 +3459,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Rikligt till måttligt i en radie av ca 50 meter  1 bild gren i förgrund</t>
+          <t>2 bild, tall med gran till vänster.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3489,7 +3489,7 @@
         <v>131198787</v>
       </c>
       <c r="B30" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3591,7 +3591,7 @@
         <v>131197782</v>
       </c>
       <c r="B31" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>

--- a/artfynd/A 2762-2026 artfynd.xlsx
+++ b/artfynd/A 2762-2026 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131197800</v>
+        <v>131199510</v>
       </c>
       <c r="B2" t="n">
-        <v>79872</v>
+        <v>79254</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>465938</v>
+        <v>465892</v>
       </c>
       <c r="R2" t="n">
-        <v>6789021</v>
+        <v>6789046</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -746,6 +746,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2026-02-17</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Rikligt till måttligt i en radie av ca 50 meter, synfältet</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -772,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131199510</v>
+        <v>131197800</v>
       </c>
       <c r="B3" t="n">
-        <v>79253</v>
+        <v>79873</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +788,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>465892</v>
+        <v>465938</v>
       </c>
       <c r="R3" t="n">
-        <v>6789046</v>
+        <v>6789021</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -843,11 +848,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2026-02-17</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Rikligt till måttligt i en radie av ca 50 meter, synfältet</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -877,7 +877,7 @@
         <v>131198193</v>
       </c>
       <c r="B4" t="n">
-        <v>79872</v>
+        <v>79873</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
         <v>131198456</v>
       </c>
       <c r="B5" t="n">
-        <v>79010</v>
+        <v>79011</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
         <v>131197802</v>
       </c>
       <c r="B6" t="n">
-        <v>57888</v>
+        <v>57889</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1170,10 +1170,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131198844</v>
+        <v>131198466</v>
       </c>
       <c r="B7" t="n">
-        <v>79253</v>
+        <v>79844</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1181,21 +1181,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1205,10 +1205,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>466309</v>
+        <v>466092</v>
       </c>
       <c r="R7" t="n">
-        <v>6789077</v>
+        <v>6789074</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1267,10 +1267,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131198466</v>
+        <v>131198844</v>
       </c>
       <c r="B8" t="n">
-        <v>79843</v>
+        <v>79254</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1278,21 +1278,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1302,10 +1302,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>466092</v>
+        <v>466309</v>
       </c>
       <c r="R8" t="n">
-        <v>6789074</v>
+        <v>6789077</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1367,7 +1367,7 @@
         <v>131198462</v>
       </c>
       <c r="B9" t="n">
-        <v>79872</v>
+        <v>79873</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1461,10 +1461,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131197848</v>
+        <v>131198869</v>
       </c>
       <c r="B10" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1496,10 +1496,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>465971</v>
+        <v>466309</v>
       </c>
       <c r="R10" t="n">
-        <v>6788983</v>
+        <v>6789065</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1558,10 +1558,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131198869</v>
+        <v>131197848</v>
       </c>
       <c r="B11" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1593,10 +1593,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>466309</v>
+        <v>465971</v>
       </c>
       <c r="R11" t="n">
-        <v>6789065</v>
+        <v>6788983</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1658,7 +1658,7 @@
         <v>131197946</v>
       </c>
       <c r="B12" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1755,7 +1755,7 @@
         <v>131199405</v>
       </c>
       <c r="B13" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1959,7 +1959,7 @@
         <v>131198192</v>
       </c>
       <c r="B15" t="n">
-        <v>79843</v>
+        <v>79844</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2056,7 +2056,7 @@
         <v>131197889</v>
       </c>
       <c r="B16" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2150,10 +2150,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131198252</v>
+        <v>131198195</v>
       </c>
       <c r="B17" t="n">
-        <v>79253</v>
+        <v>57889</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2161,34 +2161,39 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Svalkestjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>466111</v>
+        <v>466050</v>
       </c>
       <c r="R17" t="n">
-        <v>6789063</v>
+        <v>6788971</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2247,10 +2252,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131198195</v>
+        <v>131198252</v>
       </c>
       <c r="B18" t="n">
-        <v>57888</v>
+        <v>79254</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2258,39 +2263,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Svalkestjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>466050</v>
+        <v>466111</v>
       </c>
       <c r="R18" t="n">
-        <v>6788971</v>
+        <v>6789063</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2454,7 +2454,7 @@
         <v>131197847</v>
       </c>
       <c r="B20" t="n">
-        <v>57888</v>
+        <v>57889</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2556,7 +2556,7 @@
         <v>131198708</v>
       </c>
       <c r="B21" t="n">
-        <v>79843</v>
+        <v>79844</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2658,7 +2658,7 @@
         <v>131198867</v>
       </c>
       <c r="B22" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2765,7 +2765,7 @@
         <v>131198842</v>
       </c>
       <c r="B23" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2872,7 +2872,7 @@
         <v>131197797</v>
       </c>
       <c r="B24" t="n">
-        <v>79843</v>
+        <v>79844</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2974,7 +2974,7 @@
         <v>131198447</v>
       </c>
       <c r="B25" t="n">
-        <v>79011</v>
+        <v>79012</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3076,7 +3076,7 @@
         <v>131198249</v>
       </c>
       <c r="B26" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3277,10 +3277,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131198231</v>
+        <v>131199091</v>
       </c>
       <c r="B28" t="n">
-        <v>79253</v>
+        <v>57892</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3288,37 +3288,42 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Svalkestjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>466052</v>
+        <v>466114</v>
       </c>
       <c r="R28" t="n">
-        <v>6789006</v>
+        <v>6788962</v>
       </c>
       <c r="S28" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3352,7 +3357,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Rikligt till måttligt i en radie av ca 50 meter  1 bild gren i förgrund</t>
+          <t>2 bild, tall med gran till vänster.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3379,10 +3384,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131199091</v>
+        <v>131198231</v>
       </c>
       <c r="B29" t="n">
-        <v>57891</v>
+        <v>79254</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3390,42 +3395,37 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Svalkestjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>466114</v>
+        <v>466052</v>
       </c>
       <c r="R29" t="n">
-        <v>6788962</v>
+        <v>6789006</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3459,7 +3459,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>2 bild, tall med gran till vänster.</t>
+          <t>Rikligt till måttligt i en radie av ca 50 meter  1 bild gren i förgrund</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3489,7 +3489,7 @@
         <v>131198787</v>
       </c>
       <c r="B30" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3591,7 +3591,7 @@
         <v>131197782</v>
       </c>
       <c r="B31" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>

--- a/artfynd/A 2762-2026 artfynd.xlsx
+++ b/artfynd/A 2762-2026 artfynd.xlsx
@@ -1068,10 +1068,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131197802</v>
+        <v>131198466</v>
       </c>
       <c r="B6" t="n">
-        <v>57889</v>
+        <v>79844</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1079,39 +1079,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>229821</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Svalkestjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>465938</v>
+        <v>466092</v>
       </c>
       <c r="R6" t="n">
-        <v>6789021</v>
+        <v>6789074</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1170,10 +1165,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131198466</v>
+        <v>131198844</v>
       </c>
       <c r="B7" t="n">
-        <v>79844</v>
+        <v>79254</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1181,21 +1176,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1205,10 +1200,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>466092</v>
+        <v>466309</v>
       </c>
       <c r="R7" t="n">
-        <v>6789074</v>
+        <v>6789077</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1267,10 +1262,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131198844</v>
+        <v>131197802</v>
       </c>
       <c r="B8" t="n">
-        <v>79254</v>
+        <v>57889</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1278,34 +1273,39 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Svalkestjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>466309</v>
+        <v>465938</v>
       </c>
       <c r="R8" t="n">
-        <v>6789077</v>
+        <v>6789021</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -2150,10 +2150,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131198195</v>
+        <v>131198252</v>
       </c>
       <c r="B17" t="n">
-        <v>57889</v>
+        <v>79254</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2161,39 +2161,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Svalkestjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>466050</v>
+        <v>466111</v>
       </c>
       <c r="R17" t="n">
-        <v>6788971</v>
+        <v>6789063</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2252,10 +2247,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131198252</v>
+        <v>131198195</v>
       </c>
       <c r="B18" t="n">
-        <v>79254</v>
+        <v>57889</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2263,34 +2258,39 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Svalkestjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>466111</v>
+        <v>466050</v>
       </c>
       <c r="R18" t="n">
-        <v>6789063</v>
+        <v>6788971</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>

--- a/artfynd/A 2762-2026 artfynd.xlsx
+++ b/artfynd/A 2762-2026 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131199510</v>
+        <v>131197800</v>
       </c>
       <c r="B2" t="n">
-        <v>79254</v>
+        <v>79879</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>465892</v>
+        <v>465938</v>
       </c>
       <c r="R2" t="n">
-        <v>6789046</v>
+        <v>6789021</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -746,11 +746,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2026-02-17</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Rikligt till måttligt i en radie av ca 50 meter, synfältet</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131197800</v>
+        <v>131199510</v>
       </c>
       <c r="B3" t="n">
-        <v>79873</v>
+        <v>79260</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -788,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -812,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>465938</v>
+        <v>465892</v>
       </c>
       <c r="R3" t="n">
-        <v>6789021</v>
+        <v>6789046</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -848,6 +843,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2026-02-17</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Rikligt till måttligt i en radie av ca 50 meter, synfältet</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -877,7 +877,7 @@
         <v>131198193</v>
       </c>
       <c r="B4" t="n">
-        <v>79873</v>
+        <v>79879</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
         <v>131198456</v>
       </c>
       <c r="B5" t="n">
-        <v>79011</v>
+        <v>79017</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
         <v>131198466</v>
       </c>
       <c r="B6" t="n">
-        <v>79844</v>
+        <v>79850</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1165,10 +1165,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131198844</v>
+        <v>131197802</v>
       </c>
       <c r="B7" t="n">
-        <v>79254</v>
+        <v>57895</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1176,34 +1176,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Svalkestjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>466309</v>
+        <v>465938</v>
       </c>
       <c r="R7" t="n">
-        <v>6789077</v>
+        <v>6789021</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1262,10 +1267,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131197802</v>
+        <v>131198844</v>
       </c>
       <c r="B8" t="n">
-        <v>57889</v>
+        <v>79260</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1273,39 +1278,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Svalkestjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>465938</v>
+        <v>466309</v>
       </c>
       <c r="R8" t="n">
-        <v>6789021</v>
+        <v>6789077</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1367,7 +1367,7 @@
         <v>131198462</v>
       </c>
       <c r="B9" t="n">
-        <v>79873</v>
+        <v>79879</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1461,10 +1461,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131198869</v>
+        <v>131197848</v>
       </c>
       <c r="B10" t="n">
-        <v>79254</v>
+        <v>79260</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1496,10 +1496,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>466309</v>
+        <v>465971</v>
       </c>
       <c r="R10" t="n">
-        <v>6789065</v>
+        <v>6788983</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1558,10 +1558,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131197848</v>
+        <v>131198869</v>
       </c>
       <c r="B11" t="n">
-        <v>79254</v>
+        <v>79260</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1593,10 +1593,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>465971</v>
+        <v>466309</v>
       </c>
       <c r="R11" t="n">
-        <v>6788983</v>
+        <v>6789065</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1658,7 +1658,7 @@
         <v>131197946</v>
       </c>
       <c r="B12" t="n">
-        <v>79254</v>
+        <v>79260</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1755,7 +1755,7 @@
         <v>131199405</v>
       </c>
       <c r="B13" t="n">
-        <v>79254</v>
+        <v>79260</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1959,7 +1959,7 @@
         <v>131198192</v>
       </c>
       <c r="B15" t="n">
-        <v>79844</v>
+        <v>79850</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2056,7 +2056,7 @@
         <v>131197889</v>
       </c>
       <c r="B16" t="n">
-        <v>79254</v>
+        <v>79260</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2150,10 +2150,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131198252</v>
+        <v>131198195</v>
       </c>
       <c r="B17" t="n">
-        <v>79254</v>
+        <v>57895</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2161,34 +2161,39 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Svalkestjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>466111</v>
+        <v>466050</v>
       </c>
       <c r="R17" t="n">
-        <v>6789063</v>
+        <v>6788971</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2247,10 +2252,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131198195</v>
+        <v>131198252</v>
       </c>
       <c r="B18" t="n">
-        <v>57889</v>
+        <v>79260</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2258,39 +2263,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Svalkestjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>466050</v>
+        <v>466111</v>
       </c>
       <c r="R18" t="n">
-        <v>6788971</v>
+        <v>6789063</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2454,7 +2454,7 @@
         <v>131197847</v>
       </c>
       <c r="B20" t="n">
-        <v>57889</v>
+        <v>57895</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2556,7 +2556,7 @@
         <v>131198708</v>
       </c>
       <c r="B21" t="n">
-        <v>79844</v>
+        <v>79850</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2658,7 +2658,7 @@
         <v>131198867</v>
       </c>
       <c r="B22" t="n">
-        <v>57892</v>
+        <v>57898</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2765,7 +2765,7 @@
         <v>131198842</v>
       </c>
       <c r="B23" t="n">
-        <v>57892</v>
+        <v>57898</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2872,7 +2872,7 @@
         <v>131197797</v>
       </c>
       <c r="B24" t="n">
-        <v>79844</v>
+        <v>79850</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2974,7 +2974,7 @@
         <v>131198447</v>
       </c>
       <c r="B25" t="n">
-        <v>79012</v>
+        <v>79018</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3076,7 +3076,7 @@
         <v>131198249</v>
       </c>
       <c r="B26" t="n">
-        <v>57892</v>
+        <v>57898</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3277,10 +3277,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131199091</v>
+        <v>131198231</v>
       </c>
       <c r="B28" t="n">
-        <v>57892</v>
+        <v>79260</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3288,42 +3288,37 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Svalkestjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>466114</v>
+        <v>466052</v>
       </c>
       <c r="R28" t="n">
-        <v>6788962</v>
+        <v>6789006</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3357,7 +3352,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>2 bild, tall med gran till vänster.</t>
+          <t>Rikligt till måttligt i en radie av ca 50 meter  1 bild gren i förgrund</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3384,10 +3379,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131198231</v>
+        <v>131199091</v>
       </c>
       <c r="B29" t="n">
-        <v>79254</v>
+        <v>57898</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3395,37 +3390,42 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Svalkestjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>466052</v>
+        <v>466114</v>
       </c>
       <c r="R29" t="n">
-        <v>6789006</v>
+        <v>6788962</v>
       </c>
       <c r="S29" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3459,7 +3459,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Rikligt till måttligt i en radie av ca 50 meter  1 bild gren i förgrund</t>
+          <t>2 bild, tall med gran till vänster.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3489,7 +3489,7 @@
         <v>131198787</v>
       </c>
       <c r="B30" t="n">
-        <v>79254</v>
+        <v>79260</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3591,7 +3591,7 @@
         <v>131197782</v>
       </c>
       <c r="B31" t="n">
-        <v>79254</v>
+        <v>79260</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>

--- a/artfynd/A 2762-2026 artfynd.xlsx
+++ b/artfynd/A 2762-2026 artfynd.xlsx
@@ -1461,7 +1461,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131197848</v>
+        <v>131198869</v>
       </c>
       <c r="B10" t="n">
         <v>79260</v>
@@ -1496,10 +1496,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>465971</v>
+        <v>466309</v>
       </c>
       <c r="R10" t="n">
-        <v>6788983</v>
+        <v>6789065</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1558,7 +1558,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131198869</v>
+        <v>131197848</v>
       </c>
       <c r="B11" t="n">
         <v>79260</v>
@@ -1593,10 +1593,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>466309</v>
+        <v>465971</v>
       </c>
       <c r="R11" t="n">
-        <v>6789065</v>
+        <v>6788983</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -3486,7 +3486,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131198787</v>
+        <v>131197782</v>
       </c>
       <c r="B30" t="n">
         <v>79260</v>
@@ -3521,10 +3521,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>466290</v>
+        <v>465938</v>
       </c>
       <c r="R30" t="n">
-        <v>6789094</v>
+        <v>6789011</v>
       </c>
       <c r="S30" t="n">
         <v>50</v>
@@ -3561,7 +3561,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Rikligt i en radie av ca 50 meter  1 bild</t>
+          <t>Rikligt till måttligt i en radie av ca 50 meter. 3 bilder på tallar</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3588,7 +3588,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131197782</v>
+        <v>131198787</v>
       </c>
       <c r="B31" t="n">
         <v>79260</v>
@@ -3623,10 +3623,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>465938</v>
+        <v>466290</v>
       </c>
       <c r="R31" t="n">
-        <v>6789011</v>
+        <v>6789094</v>
       </c>
       <c r="S31" t="n">
         <v>50</v>
@@ -3663,7 +3663,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Rikligt till måttligt i en radie av ca 50 meter. 3 bilder på tallar</t>
+          <t>Rikligt i en radie av ca 50 meter  1 bild</t>
         </is>
       </c>
       <c r="AD31" t="b">

--- a/artfynd/A 2762-2026 artfynd.xlsx
+++ b/artfynd/A 2762-2026 artfynd.xlsx
@@ -1068,10 +1068,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131198466</v>
+        <v>131197802</v>
       </c>
       <c r="B6" t="n">
-        <v>79850</v>
+        <v>57895</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1079,34 +1079,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>229821</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Svalkestjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>466092</v>
+        <v>465938</v>
       </c>
       <c r="R6" t="n">
-        <v>6789074</v>
+        <v>6789021</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1165,10 +1170,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131197802</v>
+        <v>131198844</v>
       </c>
       <c r="B7" t="n">
-        <v>57895</v>
+        <v>79260</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1176,39 +1181,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Svalkestjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>465938</v>
+        <v>466309</v>
       </c>
       <c r="R7" t="n">
-        <v>6789021</v>
+        <v>6789077</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1267,10 +1267,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131198844</v>
+        <v>131198466</v>
       </c>
       <c r="B8" t="n">
-        <v>79260</v>
+        <v>79850</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1278,21 +1278,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1302,10 +1302,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>466309</v>
+        <v>466092</v>
       </c>
       <c r="R8" t="n">
-        <v>6789077</v>
+        <v>6789074</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -3277,10 +3277,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131198231</v>
+        <v>131199091</v>
       </c>
       <c r="B28" t="n">
-        <v>79260</v>
+        <v>57898</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3288,37 +3288,42 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Svalkestjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>466052</v>
+        <v>466114</v>
       </c>
       <c r="R28" t="n">
-        <v>6789006</v>
+        <v>6788962</v>
       </c>
       <c r="S28" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3352,7 +3357,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Rikligt till måttligt i en radie av ca 50 meter  1 bild gren i förgrund</t>
+          <t>2 bild, tall med gran till vänster.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3379,10 +3384,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131199091</v>
+        <v>131198231</v>
       </c>
       <c r="B29" t="n">
-        <v>57898</v>
+        <v>79260</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3390,42 +3395,37 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Svalkestjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>466114</v>
+        <v>466052</v>
       </c>
       <c r="R29" t="n">
-        <v>6788962</v>
+        <v>6789006</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3459,7 +3459,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>2 bild, tall med gran till vänster.</t>
+          <t>Rikligt till måttligt i en radie av ca 50 meter  1 bild gren i förgrund</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3486,7 +3486,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131197782</v>
+        <v>131198787</v>
       </c>
       <c r="B30" t="n">
         <v>79260</v>
@@ -3521,10 +3521,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>465938</v>
+        <v>466290</v>
       </c>
       <c r="R30" t="n">
-        <v>6789011</v>
+        <v>6789094</v>
       </c>
       <c r="S30" t="n">
         <v>50</v>
@@ -3561,7 +3561,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Rikligt till måttligt i en radie av ca 50 meter. 3 bilder på tallar</t>
+          <t>Rikligt i en radie av ca 50 meter  1 bild</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3588,7 +3588,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131198787</v>
+        <v>131197782</v>
       </c>
       <c r="B31" t="n">
         <v>79260</v>
@@ -3623,10 +3623,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>466290</v>
+        <v>465938</v>
       </c>
       <c r="R31" t="n">
-        <v>6789094</v>
+        <v>6789011</v>
       </c>
       <c r="S31" t="n">
         <v>50</v>
@@ -3663,7 +3663,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Rikligt i en radie av ca 50 meter  1 bild</t>
+          <t>Rikligt till måttligt i en radie av ca 50 meter. 3 bilder på tallar</t>
         </is>
       </c>
       <c r="AD31" t="b">

--- a/artfynd/A 2762-2026 artfynd.xlsx
+++ b/artfynd/A 2762-2026 artfynd.xlsx
@@ -1068,10 +1068,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131197802</v>
+        <v>131198844</v>
       </c>
       <c r="B6" t="n">
-        <v>57895</v>
+        <v>79260</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1079,39 +1079,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Svalkestjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>465938</v>
+        <v>466309</v>
       </c>
       <c r="R6" t="n">
-        <v>6789021</v>
+        <v>6789077</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1170,10 +1165,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131198844</v>
+        <v>131197802</v>
       </c>
       <c r="B7" t="n">
-        <v>79260</v>
+        <v>57895</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1181,34 +1176,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Svalkestjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>466309</v>
+        <v>465938</v>
       </c>
       <c r="R7" t="n">
-        <v>6789077</v>
+        <v>6789021</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>

--- a/artfynd/A 2762-2026 artfynd.xlsx
+++ b/artfynd/A 2762-2026 artfynd.xlsx
@@ -3073,53 +3073,48 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131198249</v>
+        <v>131197961</v>
       </c>
       <c r="B26" t="n">
-        <v>57898</v>
+        <v>8453</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>106545</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Svalkestjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>466111</v>
+        <v>466023</v>
       </c>
       <c r="R26" t="n">
-        <v>6789063</v>
+        <v>6788957</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3149,11 +3144,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2026-02-17</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>2 bild. Avbarkad gran</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3180,48 +3170,53 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131197961</v>
+        <v>131198249</v>
       </c>
       <c r="B27" t="n">
-        <v>8453</v>
+        <v>57898</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>106545</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Svalkestjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>466023</v>
+        <v>466111</v>
       </c>
       <c r="R27" t="n">
-        <v>6788957</v>
+        <v>6789063</v>
       </c>
       <c r="S27" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3251,6 +3246,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2026-02-17</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>2 bild. Avbarkad gran</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3277,10 +3277,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131199091</v>
+        <v>131198231</v>
       </c>
       <c r="B28" t="n">
-        <v>57898</v>
+        <v>79260</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3288,42 +3288,37 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Svalkestjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>466114</v>
+        <v>466052</v>
       </c>
       <c r="R28" t="n">
-        <v>6788962</v>
+        <v>6789006</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3357,7 +3352,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>2 bild, tall med gran till vänster.</t>
+          <t>Rikligt till måttligt i en radie av ca 50 meter  1 bild gren i förgrund</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3384,10 +3379,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131198231</v>
+        <v>131199091</v>
       </c>
       <c r="B29" t="n">
-        <v>79260</v>
+        <v>57898</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3395,37 +3390,42 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Svalkestjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>466052</v>
+        <v>466114</v>
       </c>
       <c r="R29" t="n">
-        <v>6789006</v>
+        <v>6788962</v>
       </c>
       <c r="S29" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3459,7 +3459,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Rikligt till måttligt i en radie av ca 50 meter  1 bild gren i förgrund</t>
+          <t>2 bild, tall med gran till vänster.</t>
         </is>
       </c>
       <c r="AD29" t="b">

--- a/artfynd/A 2762-2026 artfynd.xlsx
+++ b/artfynd/A 2762-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY31"/>
+  <dimension ref="A1:AY37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131197800</v>
+        <v>131197729</v>
       </c>
       <c r="B2" t="n">
-        <v>79879</v>
+        <v>79327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>465938</v>
+        <v>465905</v>
       </c>
       <c r="R2" t="n">
-        <v>6789021</v>
+        <v>6788998</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,14 +772,14 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131199510</v>
+        <v>131197752</v>
       </c>
       <c r="B3" t="n">
-        <v>79260</v>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>465892</v>
+        <v>465915</v>
       </c>
       <c r="R3" t="n">
-        <v>6789046</v>
+        <v>6789001</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -843,11 +843,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2026-02-17</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Rikligt till måttligt i en radie av ca 50 meter, synfältet</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -874,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131198193</v>
+        <v>131197782</v>
       </c>
       <c r="B4" t="n">
-        <v>79879</v>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -909,13 +904,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>466050</v>
+        <v>465938</v>
       </c>
       <c r="R4" t="n">
-        <v>6788971</v>
+        <v>6789011</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -945,6 +940,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2026-02-17</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Rikligt till måttligt i en radie av ca 50 meter. 3 bilder på tallar</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -971,32 +971,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131198456</v>
+        <v>131197848</v>
       </c>
       <c r="B5" t="n">
-        <v>79017</v>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1006,10 +1006,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>466092</v>
+        <v>465971</v>
       </c>
       <c r="R5" t="n">
-        <v>6789074</v>
+        <v>6788983</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1068,14 +1068,14 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131198844</v>
+        <v>131197889</v>
       </c>
       <c r="B6" t="n">
-        <v>79260</v>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1103,10 +1103,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>466309</v>
+        <v>466019</v>
       </c>
       <c r="R6" t="n">
-        <v>6789077</v>
+        <v>6789009</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1165,53 +1165,48 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131197802</v>
+        <v>131197924</v>
       </c>
       <c r="B7" t="n">
-        <v>57895</v>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Svalkestjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>465938</v>
+        <v>466023</v>
       </c>
       <c r="R7" t="n">
-        <v>6789021</v>
+        <v>6788957</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1241,6 +1236,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2026-02-17</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Rikligt till måttligt i en radie av ca 50 meter</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1267,32 +1267,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131198466</v>
+        <v>131198025</v>
       </c>
       <c r="B8" t="n">
-        <v>79850</v>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1302,10 +1302,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>466092</v>
+        <v>466033</v>
       </c>
       <c r="R8" t="n">
-        <v>6789074</v>
+        <v>6788905</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1364,32 +1364,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131198462</v>
+        <v>131198231</v>
       </c>
       <c r="B9" t="n">
-        <v>79879</v>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1399,13 +1399,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>466092</v>
+        <v>466052</v>
       </c>
       <c r="R9" t="n">
-        <v>6789074</v>
+        <v>6789006</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1435,6 +1435,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2026-02-17</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Rikligt till måttligt i en radie av ca 50 meter  1 bild gren i förgrund</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1461,14 +1466,14 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131198869</v>
+        <v>131198252</v>
       </c>
       <c r="B10" t="n">
-        <v>79260</v>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -1496,10 +1501,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>466309</v>
+        <v>466111</v>
       </c>
       <c r="R10" t="n">
-        <v>6789065</v>
+        <v>6789063</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1558,14 +1563,14 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131197848</v>
+        <v>131198787</v>
       </c>
       <c r="B11" t="n">
-        <v>79260</v>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -1593,13 +1598,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>465971</v>
+        <v>466290</v>
       </c>
       <c r="R11" t="n">
-        <v>6788983</v>
+        <v>6789094</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1629,6 +1634,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2026-02-17</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Rikligt i en radie av ca 50 meter  1 bild</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1655,14 +1665,14 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131197946</v>
+        <v>131199098</v>
       </c>
       <c r="B12" t="n">
-        <v>79260</v>
+        <v>79327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -1690,13 +1700,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>466023</v>
+        <v>466114</v>
       </c>
       <c r="R12" t="n">
-        <v>6788957</v>
+        <v>6788962</v>
       </c>
       <c r="S12" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1752,14 +1762,14 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131199405</v>
+        <v>131199510</v>
       </c>
       <c r="B13" t="n">
-        <v>79260</v>
+        <v>79327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -1787,10 +1797,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>466114</v>
+        <v>465892</v>
       </c>
       <c r="R13" t="n">
-        <v>6788962</v>
+        <v>6789046</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1823,6 +1833,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2026-02-17</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Rikligt till måttligt i en radie av ca 50 meter, synfältet</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1849,50 +1864,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131199508</v>
+        <v>131198456</v>
       </c>
       <c r="B14" t="n">
-        <v>8453</v>
+        <v>79084</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>106545</v>
+        <v>6446</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Svalkestjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>465892</v>
+        <v>466092</v>
       </c>
       <c r="R14" t="n">
-        <v>6789046</v>
+        <v>6789074</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1925,11 +1935,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2026-02-17</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>1 bild, garn i bakgrund</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1956,10 +1961,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131198192</v>
+        <v>131197800</v>
       </c>
       <c r="B15" t="n">
-        <v>79850</v>
+        <v>79946</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1967,21 +1972,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1991,10 +1996,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>466050</v>
+        <v>465938</v>
       </c>
       <c r="R15" t="n">
-        <v>6788971</v>
+        <v>6789021</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2053,10 +2058,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131197889</v>
+        <v>131198193</v>
       </c>
       <c r="B16" t="n">
-        <v>79260</v>
+        <v>79946</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2064,21 +2069,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2088,10 +2093,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>466019</v>
+        <v>466050</v>
       </c>
       <c r="R16" t="n">
-        <v>6789009</v>
+        <v>6788971</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2150,10 +2155,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131198195</v>
+        <v>131198462</v>
       </c>
       <c r="B17" t="n">
-        <v>57895</v>
+        <v>79946</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2161,39 +2166,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Svalkestjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>466050</v>
+        <v>466092</v>
       </c>
       <c r="R17" t="n">
-        <v>6788971</v>
+        <v>6789074</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2252,45 +2252,50 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131198252</v>
+        <v>131197802</v>
       </c>
       <c r="B18" t="n">
-        <v>79260</v>
+        <v>57950</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Svalkestjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>466111</v>
+        <v>465938</v>
       </c>
       <c r="R18" t="n">
-        <v>6789063</v>
+        <v>6789021</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2349,10 +2354,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131197888</v>
+        <v>131197847</v>
       </c>
       <c r="B19" t="n">
-        <v>8453</v>
+        <v>57950</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2360,27 +2365,27 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2389,10 +2394,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>466019</v>
+        <v>465971</v>
       </c>
       <c r="R19" t="n">
-        <v>6789009</v>
+        <v>6788983</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2451,14 +2456,14 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131197847</v>
+        <v>131198195</v>
       </c>
       <c r="B20" t="n">
-        <v>57895</v>
+        <v>57950</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
@@ -2482,7 +2487,7 @@
       <c r="I20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2491,10 +2496,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>465971</v>
+        <v>466050</v>
       </c>
       <c r="R20" t="n">
-        <v>6788983</v>
+        <v>6788971</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2553,10 +2558,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131198708</v>
+        <v>131197718</v>
       </c>
       <c r="B21" t="n">
-        <v>79850</v>
+        <v>57953</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2564,34 +2569,39 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>229821</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Svalkestjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>466244</v>
+        <v>465905</v>
       </c>
       <c r="R21" t="n">
-        <v>6789098</v>
+        <v>6788998</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2628,7 +2638,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>1 bild, högstubbe med garn på tall i bakgr</t>
+          <t>2 bild. Gran kåda</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2655,10 +2665,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131198867</v>
+        <v>131197751</v>
       </c>
       <c r="B22" t="n">
-        <v>57898</v>
+        <v>57953</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2686,7 +2696,7 @@
       <c r="I22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -2695,10 +2705,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>466309</v>
+        <v>465915</v>
       </c>
       <c r="R22" t="n">
-        <v>6789065</v>
+        <v>6789001</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2735,7 +2745,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>2 bild, rikligt med ringhack på tall</t>
+          <t>2 bild. Tall</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2762,10 +2772,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131198842</v>
+        <v>131198022</v>
       </c>
       <c r="B23" t="n">
-        <v>57898</v>
+        <v>57953</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2793,7 +2803,7 @@
       <c r="I23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -2802,10 +2812,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>466309</v>
+        <v>466033</v>
       </c>
       <c r="R23" t="n">
-        <v>6789077</v>
+        <v>6788905</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2842,7 +2852,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>1 bild, garn i bakgrund</t>
+          <t>1 bild, tall</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2869,10 +2879,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131197797</v>
+        <v>131198249</v>
       </c>
       <c r="B24" t="n">
-        <v>79850</v>
+        <v>57953</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2880,34 +2890,39 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>229821</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Svalkestjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>465938</v>
+        <v>466111</v>
       </c>
       <c r="R24" t="n">
-        <v>6789021</v>
+        <v>6789063</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2944,7 +2959,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>1 bild. Högstubbe, spikar?</t>
+          <t>2 bild. Avbarkad gran</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -2971,10 +2986,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131198447</v>
+        <v>131199091</v>
       </c>
       <c r="B25" t="n">
-        <v>79018</v>
+        <v>57953</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2982,34 +2997,39 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Svalkestjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>466092</v>
+        <v>466114</v>
       </c>
       <c r="R25" t="n">
-        <v>6789074</v>
+        <v>6788962</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3046,7 +3066,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>1 bild högstubbe</t>
+          <t>2 bild, tall med gran till vänster.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3073,10 +3093,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131197961</v>
+        <v>131197888</v>
       </c>
       <c r="B26" t="n">
-        <v>8453</v>
+        <v>8455</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3102,19 +3122,24 @@
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Svalkestjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>466023</v>
+        <v>466019</v>
       </c>
       <c r="R26" t="n">
-        <v>6788957</v>
+        <v>6789009</v>
       </c>
       <c r="S26" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3170,53 +3195,48 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131198249</v>
+        <v>131197961</v>
       </c>
       <c r="B27" t="n">
-        <v>57898</v>
+        <v>8455</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>106545</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Svalkestjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>466111</v>
+        <v>466023</v>
       </c>
       <c r="R27" t="n">
-        <v>6789063</v>
+        <v>6788957</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3246,11 +3266,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2026-02-17</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>2 bild. Avbarkad gran</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3277,48 +3292,53 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131198231</v>
+        <v>131199508</v>
       </c>
       <c r="B28" t="n">
-        <v>79260</v>
+        <v>8455</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Svalkestjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>466052</v>
+        <v>465892</v>
       </c>
       <c r="R28" t="n">
-        <v>6789006</v>
+        <v>6789046</v>
       </c>
       <c r="S28" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3352,7 +3372,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Rikligt till måttligt i en radie av ca 50 meter  1 bild gren i förgrund</t>
+          <t>1 bild, garn i bakgrund</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3379,10 +3399,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131199091</v>
+        <v>131198447</v>
       </c>
       <c r="B29" t="n">
-        <v>57898</v>
+        <v>79085</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3390,39 +3410,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Svalkestjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>466114</v>
+        <v>466092</v>
       </c>
       <c r="R29" t="n">
-        <v>6788962</v>
+        <v>6789074</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3459,7 +3474,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>2 bild, tall med gran till vänster.</t>
+          <t>1 bild högstubbe</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3486,10 +3501,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131198787</v>
+        <v>131197797</v>
       </c>
       <c r="B30" t="n">
-        <v>79260</v>
+        <v>79917</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3497,21 +3512,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3521,13 +3536,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>466290</v>
+        <v>465938</v>
       </c>
       <c r="R30" t="n">
-        <v>6789094</v>
+        <v>6789021</v>
       </c>
       <c r="S30" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3561,7 +3576,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Rikligt i en radie av ca 50 meter  1 bild</t>
+          <t>1 bild. Högstubbe, spikar?</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3588,10 +3603,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131197782</v>
+        <v>131198192</v>
       </c>
       <c r="B31" t="n">
-        <v>79260</v>
+        <v>79917</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3599,21 +3614,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3623,13 +3638,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>465938</v>
+        <v>466050</v>
       </c>
       <c r="R31" t="n">
-        <v>6789011</v>
+        <v>6788971</v>
       </c>
       <c r="S31" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3659,11 +3674,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2026-02-17</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Rikligt till måttligt i en radie av ca 50 meter. 3 bilder på tallar</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3687,6 +3697,613 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>131198466</v>
+      </c>
+      <c r="B32" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Svalkestjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>466092</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6789074</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2026-02-17</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2026-02-17</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>131198708</v>
+      </c>
+      <c r="B33" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Svalkestjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>466244</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6789098</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2026-02-17</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2026-02-17</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>1 bild, högstubbe med garn på tall i bakgr</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>131198844</v>
+      </c>
+      <c r="B34" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Svalkestjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>466309</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6789077</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2026-02-17</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2026-02-17</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>131198869</v>
+      </c>
+      <c r="B35" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Svalkestjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>466309</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6789065</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2026-02-17</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2026-02-17</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>131198842</v>
+      </c>
+      <c r="B36" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Svalkestjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>466309</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6789077</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2026-02-17</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2026-02-17</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>1 bild, garn i bakgrund</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>131198867</v>
+      </c>
+      <c r="B37" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Svalkestjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>466309</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6789065</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2026-02-17</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2026-02-17</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>2 bild, rikligt med ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 2762-2026 artfynd.xlsx
+++ b/artfynd/A 2762-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY37"/>
+  <dimension ref="A1:AZ37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131197729</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131197752</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -968,6 +983,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131197782</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1065,6 +1085,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131197848</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1162,6 +1187,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131197889</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1264,6 +1294,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131197924</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1361,6 +1396,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131198025</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1463,6 +1503,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131198231</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1560,6 +1605,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131198252</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1662,6 +1712,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131198787</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1759,6 +1814,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131198844</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1856,6 +1916,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131198869</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1953,6 +2018,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131199098</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2055,6 +2125,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131199510</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2152,6 +2227,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131198456</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2249,6 +2329,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131197800</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2346,6 +2431,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131198193</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2443,6 +2533,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131198462</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2545,6 +2640,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131197802</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2647,6 +2747,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131197847</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2749,6 +2854,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131198195</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2856,6 +2966,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131197718</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2963,6 +3078,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131197751</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3070,6 +3190,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131198022</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3177,6 +3302,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131198249</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3284,6 +3414,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131198842</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3391,6 +3526,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131198867</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3498,6 +3638,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131199091</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3600,6 +3745,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131197888</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3697,6 +3847,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131197961</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3804,6 +3959,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131199508</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3906,6 +4066,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131198447</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4008,6 +4173,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131197797</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4105,6 +4275,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131198192</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4202,6 +4377,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131198466</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4304,8 +4484,51 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131198708</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>